--- a/data/zenith_wellness_visualization.xlsx
+++ b/data/zenith_wellness_visualization.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>24/3/2025</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Power yoga</t>
+          <t xml:space="preserve">Power yoga </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t xml:space="preserve">Pending </t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>02-18-2025</t>
+          <t>February 18, 2025</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>02-18-2025</t>
+          <t>18-Feb-2025</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>01-23-2025</t>
+          <t>Jan 23, 2025</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>18/3/2025</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>March 2, 2025</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2-Mar-2025</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>Jan 22, 2025</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>03-20-2025</t>
+          <t>20/3/2025</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>January 4, 2025</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>12.03.2025</t>
+          <t>12-Mar-2025</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>01-24-2025</t>
+          <t>Jan 24, 2025</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>02-02-2025</t>
+          <t>2/2/2025</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>March 27, 2025</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>03-21-2025</t>
+          <t>21-Mar-2025</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>Mar 6, 2025</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>01-15-2025</t>
+          <t>15/1/2025</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>February 3, 2025</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>1-Feb-2025</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>25.02.2025</t>
+          <t>Feb 25, 2025</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>03-09-2025</t>
+          <t>9/3/2025</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>January 16, 2025</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>04.02.2025</t>
+          <t>4-Feb-2025</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>02-12-2025</t>
+          <t>Feb 12, 2025</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>13.03.2025</t>
+          <t>13/3/2025</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>03-15-2025</t>
+          <t>March 15, 2025</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">

--- a/data/zenith_wellness_visualization.xlsx
+++ b/data/zenith_wellness_visualization.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>27 Mar 2025</t>
+          <t>27/3/2025</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>24/3/2025</t>
+          <t>24-Mar-2025</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>20 Mar 2025</t>
+          <t>20.3.2025</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>March 13, 2025</t>
+          <t>13-3-2025</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>14/02/2025</t>
+          <t>14 Feb, 2025</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>February 11, 2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>February 18, 2025</t>
+          <t>18-Feb-2025</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>18-Feb-2025</t>
+          <t>18 Feb 2025</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Jan 23, 2025</t>
+          <t>23.1.2025</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2 Mar 2025</t>
+          <t>2-3-2025</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>13 Mar 2025</t>
+          <t>13 Mar, 2025</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>21/03/2025</t>
+          <t>21-Mar-2025</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>22/01/2025</t>
+          <t>22 Jan 2025</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>March 24, 2025</t>
+          <t>24.3.2025</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>March 2, 2025</t>
+          <t>2-3-2025</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2-Mar-2025</t>
+          <t>2 Mar, 2025</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Jan 22, 2025</t>
+          <t>22/1/2025</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>20 Feb 2025</t>
+          <t>20-Feb-2025</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>March 18, 2025</t>
+          <t>18.3.2025</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>12 Mar 2025</t>
+          <t>12-3-2025</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>12 Mar 2025</t>
+          <t>12 Mar, 2025</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>17 Feb 2025</t>
+          <t>17/2/2025</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>7-Jan-2025</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>7 Jan 2025</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>6 Jan 2025</t>
+          <t>6.1.2025</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>20/3/2025</t>
+          <t>20-3-2025</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2043,7 +2043,7 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1 Mar 2025</t>
+          <t>1 Mar, 2025</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>1 Jan 2025</t>
+          <t>1/1/2025</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>January 4, 2025</t>
+          <t>4-Jan-2025</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>12-Mar-2025</t>
+          <t>12.3.2025</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>18 Feb 2025</t>
+          <t>18-2-2025</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>March 19, 2025</t>
+          <t>19 Mar, 2025</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>15 Jan 2025</t>
+          <t>15/1/2025</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Jan 24, 2025</t>
+          <t>24-Jan-2025</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2/2/2025</t>
+          <t>2 Feb 2025</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>March 27, 2025</t>
+          <t>27.3.2025</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>21-Mar-2025</t>
+          <t>21-3-2025</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Mar 6, 2025</t>
+          <t>6 Mar, 2025</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>20 Feb 2025</t>
+          <t>20/2/2025</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>20 Jan 2025</t>
+          <t>20-Jan-2025</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>20 Jan 2025</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>March 21, 2025</t>
+          <t>21.3.2025</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>5-2-2025</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>January 23, 2025</t>
+          <t>23 Jan, 2025</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>January 14, 2025</t>
+          <t>14/1/2025</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>15/1/2025</t>
+          <t>15-Jan-2025</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>February 3, 2025</t>
+          <t>3 Feb 2025</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1-Feb-2025</t>
+          <t>1.2.2025</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Feb 25, 2025</t>
+          <t>25-2-2025</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>15 Jan 2025</t>
+          <t>15 Jan, 2025</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>22/01/2025</t>
+          <t>22-Jan-2025</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>January 16, 2025</t>
+          <t>16 Jan 2025</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>12 Mar 2025</t>
+          <t>12.3.2025</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>February 6, 2025</t>
+          <t>6-2-2025</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>4-Feb-2025</t>
+          <t>4 Feb, 2025</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>20 Feb 2025</t>
+          <t>20/2/2025</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>January 24, 2025</t>
+          <t>24-Jan-2025</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>March 11, 2025</t>
+          <t>11 Mar 2025</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>March 11, 2025</t>
+          <t>11.3.2025</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Feb 12, 2025</t>
+          <t>12-2-2025</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>13/3/2025</t>
+          <t>13 Mar, 2025</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>March 15, 2025</t>
+          <t>15/3/2025</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>25 Jan 2025</t>
+          <t>25-Jan-2025</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>January 2, 2025</t>
+          <t>2 Jan 2025</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
